--- a/data/processed/fmcsa_carrier_compliance.xlsx
+++ b/data/processed/fmcsa_carrier_compliance.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AEA015B3-7D32-8046-9CC5-FB8AFBA0D986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{2C9D089D-B9D6-B848-86F6-BBA1B6FDB199}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" activeTab="1" xr2:uid="{2C9D089D-B9D6-B848-86F6-BBA1B6FDB199}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -254,7 +254,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -761,7 +761,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -780,10 +780,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -837,1267 +834,9 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="237">
+  <dxfs count="60">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -2116,42 +855,6 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -2282,334 +985,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -2651,26 +1026,16 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -2679,7 +1044,286 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -2716,169 +1360,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3003,20 +1484,46 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
               <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:marker>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
@@ -3037,20 +1544,46 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
               <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:marker>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
@@ -3199,7 +1732,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3555,7 +2087,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3596,19 +2128,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3668,19 +2188,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3740,19 +2248,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3981,7 +2477,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -4362,20 +2857,46 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
               <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:marker>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -4481,7 +3002,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -7334,7 +5854,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29B91CDD-8434-6E44-AEE5-1BCF2E3B7771}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Carriers">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29B91CDD-8434-6E44-AEE5-1BCF2E3B7771}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Carriers">
   <location ref="A17:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -7458,92 +5978,92 @@
     <pageField fld="3" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Total days since inspection" fld="7" baseField="0" baseItem="0" numFmtId="173"/>
+    <dataField name="Total days since inspection" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="23">
-    <format dxfId="210">
+    <format dxfId="22">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="209">
+    <format dxfId="21">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="208">
+    <format dxfId="20">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="207">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="206">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="205">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="203">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="202">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="201">
+    <format dxfId="14">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="200">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="199">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="198">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="196">
+    <format dxfId="10">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="195">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="194">
+    <format dxfId="8">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="193">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="192">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="191">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="152">
+    <format dxfId="4">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="0"/>
     </format>
-    <format dxfId="151">
+    <format dxfId="3">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="0"/>
     </format>
-    <format dxfId="150">
+    <format dxfId="2">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="0"/>
     </format>
-    <format dxfId="149">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="79">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -7598,7 +6118,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3382FE53-BA9D-8C49-8B4F-E99DB1C0B6FD}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Safety Rating">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3382FE53-BA9D-8C49-8B4F-E99DB1C0B6FD}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Safety Rating">
   <location ref="A9:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -7650,73 +6170,73 @@
     <dataField name="Average of Out of Service %" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="236">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="234">
+    <format dxfId="40">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="233">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="232">
+    <format dxfId="38">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="231">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="230">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="229">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="227">
+    <format dxfId="34">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="226">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="225">
+    <format dxfId="32">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="224">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="223">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="222">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="220">
+    <format dxfId="28">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="219">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="218">
+    <format dxfId="26">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="217">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="216">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="215">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -7780,7 +6300,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A999658-8116-2349-A16A-D737DB5E6662}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Insurance Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A999658-8116-2349-A16A-D737DB5E6662}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Insurance Status">
   <location ref="A3:D5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -7880,70 +6400,70 @@
     <dataField name="Count of safety_rating" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="37">
+    <format dxfId="59">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="58">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="57">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="53">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="51">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="47">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="45">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -8357,13 +6877,13 @@
       <c r="A5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="1">
         <v>43</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="1">
         <v>7</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="1">
         <v>50</v>
       </c>
     </row>
@@ -8409,10 +6929,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8428,7 +6948,7 @@
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>894</v>
       </c>
     </row>
@@ -8436,7 +6956,7 @@
       <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="8">
         <v>827</v>
       </c>
     </row>
@@ -8444,7 +6964,7 @@
       <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>790</v>
       </c>
     </row>
@@ -8452,7 +6972,7 @@
       <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="8">
         <v>585</v>
       </c>
     </row>
@@ -8460,7 +6980,7 @@
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <v>433</v>
       </c>
     </row>
@@ -8468,7 +6988,7 @@
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <v>422</v>
       </c>
     </row>
@@ -8476,7 +6996,7 @@
       <c r="A24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="8">
         <v>372</v>
       </c>
     </row>
@@ -8484,7 +7004,7 @@
       <c r="A25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="8">
         <v>4323</v>
       </c>
     </row>
@@ -8558,7 +7078,7 @@
       </c>
       <c r="H2" s="4">
         <f ca="1">TODAY()-G2</f>
-        <v>895</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -8585,7 +7105,7 @@
       </c>
       <c r="H3" s="5">
         <f t="shared" ref="H3:H51" ca="1" si="0">TODAY()-G3</f>
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -8612,7 +7132,7 @@
       </c>
       <c r="H4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -8639,7 +7159,7 @@
       </c>
       <c r="H5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -8666,7 +7186,7 @@
       </c>
       <c r="H6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>843</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -8693,7 +7213,7 @@
       </c>
       <c r="H7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>705</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -8720,7 +7240,7 @@
       </c>
       <c r="H8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>665</v>
+        <v>671</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -8747,7 +7267,7 @@
       </c>
       <c r="H9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -8774,7 +7294,7 @@
       </c>
       <c r="H10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -8801,7 +7321,7 @@
       </c>
       <c r="H11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>884</v>
+        <v>890</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -8828,7 +7348,7 @@
       </c>
       <c r="H12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -8855,7 +7375,7 @@
       </c>
       <c r="H13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>838</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -8882,7 +7402,7 @@
       </c>
       <c r="H14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -8909,7 +7429,7 @@
       </c>
       <c r="H15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -8936,7 +7456,7 @@
       </c>
       <c r="H16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -8963,7 +7483,7 @@
       </c>
       <c r="H17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -8990,7 +7510,7 @@
       </c>
       <c r="H18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -9017,7 +7537,7 @@
       </c>
       <c r="H19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -9044,7 +7564,7 @@
       </c>
       <c r="H20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -9071,7 +7591,7 @@
       </c>
       <c r="H21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>791</v>
+        <v>797</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -9098,7 +7618,7 @@
       </c>
       <c r="H22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>814</v>
+        <v>820</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -9125,7 +7645,7 @@
       </c>
       <c r="H23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -9152,7 +7672,7 @@
       </c>
       <c r="H24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -9179,7 +7699,7 @@
       </c>
       <c r="H25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -9206,7 +7726,7 @@
       </c>
       <c r="H26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -9233,7 +7753,7 @@
       </c>
       <c r="H27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -9260,7 +7780,7 @@
       </c>
       <c r="H28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -9287,7 +7807,7 @@
       </c>
       <c r="H29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -9314,7 +7834,7 @@
       </c>
       <c r="H30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -9341,7 +7861,7 @@
       </c>
       <c r="H31" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -9368,7 +7888,7 @@
       </c>
       <c r="H32" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -9395,7 +7915,7 @@
       </c>
       <c r="H33" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -9422,7 +7942,7 @@
       </c>
       <c r="H34" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>918</v>
+        <v>924</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -9449,7 +7969,7 @@
       </c>
       <c r="H35" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>828</v>
+        <v>834</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -9476,7 +7996,7 @@
       </c>
       <c r="H36" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>787</v>
+        <v>793</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -9503,7 +8023,7 @@
       </c>
       <c r="H37" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -9530,7 +8050,7 @@
       </c>
       <c r="H38" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -9557,7 +8077,7 @@
       </c>
       <c r="H39" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -9584,7 +8104,7 @@
       </c>
       <c r="H40" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -9611,7 +8131,7 @@
       </c>
       <c r="H41" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -9638,7 +8158,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -9665,7 +8185,7 @@
       </c>
       <c r="H43" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>884</v>
+        <v>890</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -9692,7 +8212,7 @@
       </c>
       <c r="H44" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>893</v>
+        <v>899</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -9719,7 +8239,7 @@
       </c>
       <c r="H45" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -9746,7 +8266,7 @@
       </c>
       <c r="H46" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -9773,7 +8293,7 @@
       </c>
       <c r="H47" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -9800,7 +8320,7 @@
       </c>
       <c r="H48" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -9827,7 +8347,7 @@
       </c>
       <c r="H49" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -9854,7 +8374,7 @@
       </c>
       <c r="H50" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -9881,7 +8401,7 @@
       </c>
       <c r="H51" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>
